--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N7_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.587009906850133</v>
+        <v>1.232889109863147</v>
       </c>
       <c r="D2" t="n">
-        <v>10.28317354179436</v>
+        <v>1.671015700541583</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
